--- a/fixtures/text/kit_mini.xlsx
+++ b/fixtures/text/kit_mini.xlsx
@@ -604,6 +604,11 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>사람</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>44-LV-999</t>
@@ -669,6 +674,11 @@
       <c r="G4" t="n">
         <v>1</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AI초안(Claude)</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>11-FV-999</t>
@@ -729,6 +739,11 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>사람</t>
         </is>
       </c>
     </row>
